--- a/multiSchoolOutput/06_School_of_Biological_Sciences/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/06_School_of_Biological_Sciences/solution_weeks_9_10.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -685,7 +685,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0001_01_1.267</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -904,12 +904,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -921,7 +921,7 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -963,12 +963,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -980,7 +980,7 @@
         <v>88</v>
       </c>
       <c r="F10" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1039,7 +1039,7 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0335_02_2.4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1511,7 +1511,7 @@
         <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0254_01_1.08</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0113_00_G.13</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0283_01_1.17</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0001_02_2.347</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2396,7 +2396,7 @@
         <v>15</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0201_07_7.02</t>
+          <t>0254_01_1.10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0283_01_1.17</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2758,7 +2758,7 @@
         <v>80</v>
       </c>
       <c r="F40" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3063,7 +3063,7 @@
         <v>300</v>
       </c>
       <c r="F45" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3124,7 +3124,7 @@
         <v>85</v>
       </c>
       <c r="F46" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3168,12 +3168,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3551,7 +3551,7 @@
         <v>80</v>
       </c>
       <c r="F53" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0008_-1_B.162</t>
+          <t>0113_00_G.15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4039,7 +4039,7 @@
         <v>15</v>
       </c>
       <c r="F61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4083,12 +4083,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0219_00_G.01</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4100,7 +4100,7 @@
         <v>15</v>
       </c>
       <c r="F62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0251_01_1.02</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0228_09_9.01</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4283,7 +4283,7 @@
         <v>15</v>
       </c>
       <c r="F65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0201_02_2.11</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0103_01_1.B15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4466,7 +4466,7 @@
         <v>15</v>
       </c>
       <c r="F68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4588,7 +4588,7 @@
         <v>300</v>
       </c>
       <c r="F70" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0254_01_1.08</t>
+          <t>0228_11_11.01</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4954,7 +4954,7 @@
         <v>88</v>
       </c>
       <c r="F76" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0335_00_G.12</t>
+          <t>0227_03_3.39</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5381,7 +5381,7 @@
         <v>17</v>
       </c>
       <c r="F83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0001_02_2.345</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5564,7 +5564,7 @@
         <v>15</v>
       </c>
       <c r="F86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5686,7 +5686,7 @@
         <v>15</v>
       </c>
       <c r="F88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0228_11_11.01</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6113,7 +6113,7 @@
         <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6235,7 +6235,7 @@
         <v>80</v>
       </c>
       <c r="F97" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0254_01_1.10</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6601,7 +6601,7 @@
         <v>90</v>
       </c>
       <c r="F103" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6662,7 +6662,7 @@
         <v>80</v>
       </c>
       <c r="F104" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6767,12 +6767,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6845,7 +6845,7 @@
         <v>15</v>
       </c>
       <c r="F107" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6889,12 +6889,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6906,7 +6906,7 @@
         <v>88</v>
       </c>
       <c r="F108" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6950,12 +6950,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0228_07_7.01</t>
+          <t>0214_01_1.10</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7638,7 +7638,7 @@
         <v>300</v>
       </c>
       <c r="F120" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0001_02_2.343</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7699,7 +7699,7 @@
         <v>15</v>
       </c>
       <c r="F121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -7743,12 +7743,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0103_01_1.B15</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8353,12 +8353,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8370,7 +8370,7 @@
         <v>300</v>
       </c>
       <c r="F132" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0008_-1_B.162</t>
+          <t>0113_00_G.15</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8658,12 +8658,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8902,12 +8902,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0113_00_G.13</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0228_11_11.18</t>
+          <t>0450_03_3.52</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0335_01_1.4</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9346,7 +9346,7 @@
         <v>15</v>
       </c>
       <c r="F148" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -9512,12 +9512,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0227_03_3.03</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9956,7 +9956,7 @@
         <v>15</v>
       </c>
       <c r="F158" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
